--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -965,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -998,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1034,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1054,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1236,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1286,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1347,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1397,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1405,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1453,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1472,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1508,673 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -983,24 +983,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1125,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,33 +1153,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1236,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1314,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1347,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1371,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1497,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1508,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1647,32 +1671,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1680,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1704,33 +1732,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1841,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1952,7 +1984,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2063,7 +2095,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2071,22 +2103,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2124,7 +2156,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2138,43 +2170,955 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
+      <c r="AA16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,18 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,17 +1518,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1526,13 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1593,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1681,24 +1705,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1708,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1757,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1790,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -1823,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -1934,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,33 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2012,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2045,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2069,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,32 +2286,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2271,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2295,33 +2347,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2997,13 +3053,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3011,22 +3071,22 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3064,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,47 +3138,622 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>09:25</t>
         </is>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="inlineStr">
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
+      <c r="AA24" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>92.0</t>
         </is>
       </c>
-      <c r="AC23" s="2" t="inlineStr">
-        <is>
-          <t>6/13</t>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2405,32 +2405,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2462,37 +2466,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2520,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -2553,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2664,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,37 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2833,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2861,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2894,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2918,17 +2938,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2938,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3063,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3178,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3206,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3239,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3263,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3283,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3408,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3523,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3608,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3638,7 +3662,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3646,22 +3670,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3699,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3713,47 +3737,622 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z28" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>10/13</t>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3144,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3172,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,14 +3306,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3421,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3575,32 +3579,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3608,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3632,17 +3640,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3652,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4007,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4122,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4245,22 +4253,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4293,12 +4301,12 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4312,47 +4320,392 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>11:05</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
-      <c r="AC33" s="2" t="inlineStr">
-        <is>
-          <t>9/13</t>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3252,12 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3349,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3382,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3406,17 +3410,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3426,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3464,32 +3468,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3497,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3521,37 +3529,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3597,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3665,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3706,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3731,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3767,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3775,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3813,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3846,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,37 +3886,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3944,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3961,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,17 +4005,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4005,12 +4025,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4076,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4135,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4130,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4178,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4191,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4215,37 +4239,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4360,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4475,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4590,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4695,17 +4719,592 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>13/13</t>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3954,24 +3954,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4063,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4124,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4140,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4188,24 +4192,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>64分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4215,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,7 +4268,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4297,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4330,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4354,17 +4362,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4374,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4412,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4445,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,37 +4481,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4527,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4560,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4584,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4604,12 +4620,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4642,32 +4658,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -4675,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4699,32 +4719,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4790,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4844,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4959,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5074,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5199,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5299,12 +5319,702 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,14 +4377,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,14 +4615,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4777,32 +4777,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4834,17 +4838,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4854,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4892,32 +4896,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,17 +4957,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4969,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5007,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5040,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5084,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5122,32 +5134,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -5155,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,37 +5195,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5237,32 +5253,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5270,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5294,17 +5314,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5314,12 +5334,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5385,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5439,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5467,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5500,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5524,37 +5548,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5730,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5913,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6038,467 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5263,24 +5263,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5372,32 +5372,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5429,17 +5433,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5449,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5497,24 +5501,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5524,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5573,12 +5577,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5606,32 +5610,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,17 +5671,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5683,12 +5691,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5721,32 +5729,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5754,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,37 +5790,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5848,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5869,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,17 +5909,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5913,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5984,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,32 +6028,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6099,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6153,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6253,7 +6273,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6268,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6378,12 +6398,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6518,582 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,14 +2719,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,14 +4258,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,17 +5215,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,14 +5329,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5858,24 +5858,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5977,24 +5977,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6086,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -6119,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,17 +6147,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6163,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -6201,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6266,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6278,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6316,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6349,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,17 +6385,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6393,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6443,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6464,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,37 +6504,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6546,32 +6562,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6579,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,17 +6623,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6623,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6661,32 +6681,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -6694,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6718,37 +6742,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6858,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6963,7 +6987,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6978,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,17 +7107,707 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>77.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>11/13</t>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,14 +3544,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,14 +4972,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,14 +5924,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,17 +6286,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6453,24 +6453,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,12 +6767,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6800,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6861,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6877,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -6915,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6948,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,17 +6980,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6992,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7030,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7063,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,17 +7099,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7107,17 +7119,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -7145,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,37 +7218,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,7 +7348,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7408,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7457,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7577,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7687,12 +7703,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7700,22 +7716,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7748,12 +7764,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7767,45 +7783,735 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>16:35</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W64" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y64" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
+      <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AC68" s="2" t="inlineStr">
         <is>
           <t>8/13</t>
         </is>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,17 +6281,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7048,24 +7048,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,17 +7114,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,32 +7391,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,17 +7452,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7468,12 +7472,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,7 +7582,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7654,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8114,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8229,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8344,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8406,22 +8410,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8459,7 +8463,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8473,47 +8477,507 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>8/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>12/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,17 +5686,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7276,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7309,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,17 +7337,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7353,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7510,32 +7514,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7543,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,17 +7575,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7587,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7740,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -7773,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,32 +7809,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7888,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,7 +7939,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7970,32 +7982,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8003,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,17 +8043,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8047,17 +8063,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8233,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8348,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8463,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8622,12 +8638,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8693,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8852,17 +8868,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8870,22 +8886,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A32298D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8918,12 +8934,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8937,47 +8953,392 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>17:50</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>78.6</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
         <is>
           <t>12/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,17 +4972,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,17 +5210,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5924,17 +5924,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,17 +6162,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,22 +6638,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,17 +6876,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,17 +7357,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -7758,24 +7758,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -7867,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7900,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7944,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7992,24 +7996,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8019,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8058,7 +8062,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8068,12 +8072,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8105,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8134,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,37 +8166,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -8216,32 +8224,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8249,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,32 +8285,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8331,32 +8343,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8364,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,37 +8404,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -8446,32 +8462,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8479,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8503,32 +8523,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8561,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8594,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,17 +8642,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8638,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -8676,32 +8700,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -8709,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8733,32 +8761,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8824,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8863,7 +8891,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8939,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8988,12 +9016,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9108,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9241,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9231,22 +9259,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9284,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9323,22 +9351,827 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>4/13</t>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>11/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:52</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>7/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3425,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,17 +6281,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6519,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7114,17 +7114,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,22 +7471,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,22 +7824,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8062,22 +8062,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8591,24 +8591,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -8710,24 +8710,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8934,32 +8934,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8967,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,37 +8995,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9053,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9082,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,32 +9114,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9164,32 +9172,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9197,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,17 +9233,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9241,17 +9253,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,32 +9406,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9427,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,37 +9467,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9596,7 +9612,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -9624,32 +9640,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9657,7 +9677,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,37 +9701,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10051,7 +10071,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10064,22 +10084,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10112,12 +10132,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10161,17 +10181,477 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
         <is>
           <t>76.5</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>7/13</t>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,22 +5448,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6881,17 +6881,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,17 +8305,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8419,22 +8419,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,17 +8543,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8891,22 +8891,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9291,32 +9291,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9324,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9348,17 +9352,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9368,12 +9372,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9443,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9497,7 +9501,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -9525,32 +9529,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9558,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9582,17 +9590,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9602,17 +9610,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -9650,24 +9658,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9677,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9726,12 +9734,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9759,32 +9767,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9792,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9816,17 +9828,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9836,17 +9848,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -9874,32 +9886,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9907,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9931,37 +9947,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -9989,32 +10005,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:52</t>
@@ -10022,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10046,17 +10066,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10066,12 +10086,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10104,32 +10124,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10137,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10161,17 +10185,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10181,7 +10205,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10219,32 +10243,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10252,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10276,37 +10304,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10421,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10521,7 +10549,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10597,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10646,12 +10674,357 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>9/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-182路.xlsx
+++ b/data/export/2026-10-09-182路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7000,17 +7000,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,17 +9015,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9729,17 +9729,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10265,12 +10265,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,32 +10362,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10395,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10419,17 +10423,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10439,12 +10443,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10477,32 +10481,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -10510,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,17 +10542,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10554,17 +10562,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -10592,32 +10600,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10625,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,17 +10661,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10669,17 +10681,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10707,32 +10719,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10740,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10780,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,12 +10800,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10855,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10970,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11014,17 +11030,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
